--- a/artfynd/A 13332-2024 artfynd.xlsx
+++ b/artfynd/A 13332-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121499182</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121499193</v>
+        <v>121499187</v>
       </c>
       <c r="B3" t="n">
-        <v>91150</v>
+        <v>90678</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,25 +815,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,7 +841,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -886,11 +890,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Undersida granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121499187</v>
+        <v>121499193</v>
       </c>
       <c r="B4" t="n">
-        <v>90675</v>
+        <v>91153</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,25 +929,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -956,11 +955,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1005,6 +1000,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Undersida granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 13332-2024 artfynd.xlsx
+++ b/artfynd/A 13332-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121499182</v>
+        <v>121499187</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>90678</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Granbacken, Fällevägen 14, Frånö, Ång</t>
@@ -771,11 +762,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>4 st, inom cirkel på 50 meter.  2st nära varandra. Blommande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121499187</v>
+        <v>121499193</v>
       </c>
       <c r="B3" t="n">
-        <v>90678</v>
+        <v>91153</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,11 +827,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -890,6 +872,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Undersida granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121499193</v>
+        <v>121499182</v>
       </c>
       <c r="B4" t="n">
-        <v>91153</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,31 +920,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granbacken, Fällevägen 14, Frånö, Ång</t>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Undersida granlåga</t>
+          <t>4 st, inom cirkel på 50 meter.  2st nära varandra. Blommande</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 13332-2024 artfynd.xlsx
+++ b/artfynd/A 13332-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121499187</v>
       </c>
       <c r="B2" t="n">
-        <v>90678</v>
+        <v>90684</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>121499193</v>
       </c>
       <c r="B3" t="n">
-        <v>91153</v>
+        <v>91159</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>121499182</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 13332-2024 artfynd.xlsx
+++ b/artfynd/A 13332-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121499187</v>
       </c>
       <c r="B2" t="n">
-        <v>90684</v>
+        <v>90685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121499193</v>
+        <v>121499182</v>
       </c>
       <c r="B3" t="n">
-        <v>91159</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,31 +805,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granbacken, Fällevägen 14, Frånö, Ång</t>
@@ -876,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Undersida granlåga</t>
+          <t>4 st, inom cirkel på 50 meter.  2st nära varandra. Blommande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121499182</v>
+        <v>121499193</v>
       </c>
       <c r="B4" t="n">
-        <v>98104</v>
+        <v>91160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,44 +933,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granbacken, Fällevägen 14, Frånö, Ång</t>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>4 st, inom cirkel på 50 meter.  2st nära varandra. Blommande</t>
+          <t>Undersida granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 13332-2024 artfynd.xlsx
+++ b/artfynd/A 13332-2024 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121499182</v>
+        <v>121499193</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>91160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,44 +805,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granbacken, Fällevägen 14, Frånö, Ång</t>
@@ -889,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>4 st, inom cirkel på 50 meter.  2st nära varandra. Blommande</t>
+          <t>Undersida granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121499193</v>
+        <v>121499182</v>
       </c>
       <c r="B4" t="n">
-        <v>91160</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,31 +920,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granbacken, Fällevägen 14, Frånö, Ång</t>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Undersida granlåga</t>
+          <t>4 st, inom cirkel på 50 meter.  2st nära varandra. Blommande</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 13332-2024 artfynd.xlsx
+++ b/artfynd/A 13332-2024 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121499193</v>
+        <v>121499182</v>
       </c>
       <c r="B3" t="n">
-        <v>91160</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,31 +805,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granbacken, Fällevägen 14, Frånö, Ång</t>
@@ -876,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Undersida granlåga</t>
+          <t>4 st, inom cirkel på 50 meter.  2st nära varandra. Blommande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121499182</v>
+        <v>121499193</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>91160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,44 +933,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granbacken, Fällevägen 14, Frånö, Ång</t>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>4 st, inom cirkel på 50 meter.  2st nära varandra. Blommande</t>
+          <t>Undersida granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 13332-2024 artfynd.xlsx
+++ b/artfynd/A 13332-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121499187</v>
       </c>
       <c r="B2" t="n">
-        <v>90685</v>
+        <v>90693</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121499182</v>
+        <v>121499193</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>91168</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,44 +805,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granbacken, Fällevägen 14, Frånö, Ång</t>
@@ -889,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>4 st, inom cirkel på 50 meter.  2st nära varandra. Blommande</t>
+          <t>Undersida granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121499193</v>
+        <v>121499182</v>
       </c>
       <c r="B4" t="n">
-        <v>91160</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,31 +920,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granbacken, Fällevägen 14, Frånö, Ång</t>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Undersida granlåga</t>
+          <t>4 st, inom cirkel på 50 meter.  2st nära varandra. Blommande</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 13332-2024 artfynd.xlsx
+++ b/artfynd/A 13332-2024 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121499193</v>
+        <v>121499182</v>
       </c>
       <c r="B3" t="n">
-        <v>91168</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,31 +805,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granbacken, Fällevägen 14, Frånö, Ång</t>
@@ -876,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Undersida granlåga</t>
+          <t>4 st, inom cirkel på 50 meter.  2st nära varandra. Blommande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121499182</v>
+        <v>121499193</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>91168</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,44 +933,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granbacken, Fällevägen 14, Frånö, Ång</t>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>4 st, inom cirkel på 50 meter.  2st nära varandra. Blommande</t>
+          <t>Undersida granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 13332-2024 artfynd.xlsx
+++ b/artfynd/A 13332-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121499187</v>
+        <v>121499193</v>
       </c>
       <c r="B2" t="n">
-        <v>90693</v>
+        <v>91168</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,11 +713,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -762,6 +758,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Undersida granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -917,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121499193</v>
+        <v>121499187</v>
       </c>
       <c r="B4" t="n">
-        <v>91168</v>
+        <v>90693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,25 +930,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -955,7 +956,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1000,11 +1005,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Undersida granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 13332-2024 artfynd.xlsx
+++ b/artfynd/A 13332-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121499193</v>
+        <v>121499187</v>
       </c>
       <c r="B2" t="n">
-        <v>91168</v>
+        <v>90693</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,7 +713,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -758,11 +762,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Undersida granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121499182</v>
+        <v>121499193</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>91168</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,44 +805,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granbacken, Fällevägen 14, Frånö, Ång</t>
@@ -890,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>4 st, inom cirkel på 50 meter.  2st nära varandra. Blommande</t>
+          <t>Undersida granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121499187</v>
+        <v>121499182</v>
       </c>
       <c r="B4" t="n">
-        <v>90693</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,39 +916,48 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granbacken, Fällevägen 14, Frånö, Ång</t>
@@ -1005,6 +1000,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>4 st, inom cirkel på 50 meter.  2st nära varandra. Blommande</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 13332-2024 artfynd.xlsx
+++ b/artfynd/A 13332-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121499187</v>
+        <v>121499193</v>
       </c>
       <c r="B2" t="n">
-        <v>90693</v>
+        <v>91168</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,11 +713,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -762,6 +758,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Undersida granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121499193</v>
+        <v>121499182</v>
       </c>
       <c r="B3" t="n">
-        <v>91168</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,31 +806,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granbacken, Fällevägen 14, Frånö, Ång</t>
@@ -876,7 +890,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Undersida granlåga</t>
+          <t>4 st, inom cirkel på 50 meter.  2st nära varandra. Blommande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121499182</v>
+        <v>121499187</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>90693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,48 +930,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granbacken, Fällevägen 14, Frånö, Ång</t>
@@ -1000,11 +1005,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>4 st, inom cirkel på 50 meter.  2st nära varandra. Blommande</t>
         </is>
       </c>
       <c r="AD4" t="b">
